--- a/SWTest/AMT.xlsx
+++ b/SWTest/AMT.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\SWTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16494994-8726-4D07-90B8-DA61AB5C0739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E650B375-3A3A-4BBC-8F74-AE8D64F6907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="9870" windowWidth="16410" windowHeight="9465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="-6795" windowWidth="16410" windowHeight="28185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AMT" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AMT!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AMT!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="452">
   <si>
     <t>Dependency</t>
   </si>
@@ -526,12 +526,6 @@
   </si>
   <si>
     <t>64, 132, 133</t>
-  </si>
-  <si>
-    <t>0x0186</t>
-  </si>
-  <si>
-    <t>Unit Serial Number</t>
   </si>
   <si>
     <t>Electric Motor Rotation</t>
@@ -658,9 +652,6 @@
     <t>NO</t>
   </si>
   <si>
-    <t>YES</t>
-  </si>
-  <si>
     <t>Door Switch Configuration - Zone 1</t>
   </si>
   <si>
@@ -875,12 +866,6 @@
   </si>
   <si>
     <t>0x0387</t>
-  </si>
-  <si>
-    <t>Trailer ID</t>
-  </si>
-  <si>
-    <t>0x043C</t>
   </si>
   <si>
     <t>OSP Profile Active</t>
@@ -1218,10 +1203,6 @@
   </si>
   <si>
     <t>Delta T Defrost - Zone 1</t>
-  </si>
-  <si>
-    <t>P.Carr 14th June 22: 
-This shall be displayed/recorded in the header file of the data log only (and not as an event log).  Trailer ID &amp; Unit SN are not normal SPNs rather an array type parameter (it includes strings and numbers) so, we are unable to store the values in database if event occurs.</t>
   </si>
   <si>
     <t>P.Carr 14th June 22: 
@@ -1491,7 +1472,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1560,13 +1541,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <strike/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1574,7 +1548,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1605,6 +1579,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1618,7 +1598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1682,21 +1662,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1718,6 +1683,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2033,7 +2001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" style="5" customWidth="1"/>
@@ -2054,49 +2022,49 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="8" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2128,14 +2096,14 @@
       <c r="J2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M2" s="22" t="s">
-        <v>205</v>
+      <c r="K2" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
@@ -2169,19 +2137,19 @@
       <c r="J3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M3" s="22" t="s">
-        <v>205</v>
+      <c r="K3" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
@@ -2210,19 +2178,19 @@
       <c r="J4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M4" s="22" t="s">
-        <v>205</v>
+      <c r="K4" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>26</v>
       </c>
@@ -2251,19 +2219,19 @@
       <c r="J5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>205</v>
+      <c r="K5" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>28</v>
       </c>
@@ -2292,14 +2260,14 @@
       <c r="J6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M6" s="22" t="s">
-        <v>205</v>
+      <c r="K6" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
@@ -2327,22 +2295,22 @@
         <v>6</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M7" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K7" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="7" t="s">
@@ -2376,23 +2344,23 @@
         <v>9</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K8" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>30</v>
       </c>
@@ -2419,26 +2387,26 @@
         <v>9</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M9" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K9" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
     <row r="10" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>4</v>
@@ -2460,14 +2428,14 @@
         <v>7</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M10" s="22" t="s">
-        <v>205</v>
+      <c r="K10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7" t="s">
@@ -2476,10 +2444,10 @@
     </row>
     <row r="11" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>4</v>
@@ -2494,21 +2462,21 @@
         <v>0</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M11" s="22" t="s">
-        <v>205</v>
+      <c r="K11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7" t="s">
@@ -2520,7 +2488,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>13</v>
@@ -2538,22 +2506,22 @@
         <v>6</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M12" s="22" t="s">
-        <v>205</v>
+        <v>298</v>
+      </c>
+      <c r="K12" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="12"/>
@@ -2563,7 +2531,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>4</v>
@@ -2585,24 +2553,24 @@
         <v>7</v>
       </c>
       <c r="J13" s="6"/>
-      <c r="K13" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M13" s="22" t="s">
-        <v>205</v>
+      <c r="K13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="9"/>
     </row>
     <row r="14" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>13</v>
@@ -2620,26 +2588,26 @@
         <v>6</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M14" s="22" t="s">
-        <v>205</v>
+        <v>314</v>
+      </c>
+      <c r="K14" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="7" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2647,7 +2615,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>13</v>
@@ -2665,26 +2633,26 @@
         <v>6</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>205</v>
+        <v>314</v>
+      </c>
+      <c r="K15" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -2716,14 +2684,14 @@
       <c r="J16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K16" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M16" s="22" t="s">
-        <v>205</v>
+      <c r="K16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -2755,19 +2723,19 @@
         <v>9</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>206</v>
+        <v>312</v>
+      </c>
+      <c r="K17" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="O17" s="7"/>
     </row>
@@ -2794,32 +2762,32 @@
         <v>6</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L18" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M18" s="22" t="s">
-        <v>205</v>
+        <v>313</v>
+      </c>
+      <c r="K18" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="12"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>4</v>
@@ -2834,21 +2802,21 @@
         <v>0</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J19" s="6"/>
-      <c r="K19" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M19" s="22" t="s">
-        <v>205</v>
+      <c r="K19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -2880,14 +2848,14 @@
         <v>9</v>
       </c>
       <c r="J20" s="6"/>
-      <c r="K20" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L20" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M20" s="22" t="s">
-        <v>205</v>
+      <c r="K20" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N20"/>
       <c r="O20" s="7"/>
@@ -2919,14 +2887,14 @@
         <v>9</v>
       </c>
       <c r="J21" s="6"/>
-      <c r="K21" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M21" s="22" t="s">
-        <v>205</v>
+      <c r="K21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N21" s="7"/>
       <c r="O21" s="7" t="s">
@@ -2953,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7" t="s">
@@ -2962,18 +2930,18 @@
       <c r="J22" s="6">
         <v>159</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M22" s="22" t="s">
-        <v>205</v>
+      <c r="K22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N22" s="7"/>
       <c r="O22" s="9" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2996,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7" t="s">
@@ -3005,26 +2973,26 @@
       <c r="J23" s="6">
         <v>159</v>
       </c>
-      <c r="K23" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M23" s="22" t="s">
-        <v>205</v>
+      <c r="K23" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="9" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>4</v>
@@ -3046,14 +3014,14 @@
         <v>9</v>
       </c>
       <c r="J24" s="6"/>
-      <c r="K24" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M24" s="22" t="s">
-        <v>205</v>
+      <c r="K24" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N24" s="7"/>
       <c r="O24" s="9"/>
@@ -3063,7 +3031,7 @@
         <v>43</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>13</v>
@@ -3081,7 +3049,7 @@
         <v>6</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>9</v>
@@ -3089,14 +3057,14 @@
       <c r="J25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K25" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L25" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M25" s="22" t="s">
-        <v>205</v>
+      <c r="K25" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N25" s="4"/>
       <c r="O25" s="12"/>
@@ -3106,7 +3074,7 @@
         <v>55</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>13</v>
@@ -3124,7 +3092,7 @@
         <v>6</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>9</v>
@@ -3132,24 +3100,24 @@
       <c r="J26" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="K26" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L26" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M26" s="22" t="s">
-        <v>205</v>
+      <c r="K26" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="12"/>
     </row>
     <row r="27" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>4</v>
@@ -3173,14 +3141,14 @@
       <c r="J27" s="6">
         <v>107</v>
       </c>
-      <c r="K27" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M27" s="22" t="s">
-        <v>205</v>
+      <c r="K27" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N27" s="4"/>
       <c r="O27" s="12"/>
@@ -3190,7 +3158,7 @@
         <v>50</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>13</v>
@@ -3208,22 +3176,22 @@
         <v>6</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L28" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M28" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K28" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="7" t="s">
@@ -3235,7 +3203,7 @@
         <v>54</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>13</v>
@@ -3253,22 +3221,22 @@
         <v>6</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L29" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M29" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K29" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="7" t="s">
@@ -3277,10 +3245,10 @@
     </row>
     <row r="30" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>4</v>
@@ -3302,24 +3270,24 @@
         <v>9</v>
       </c>
       <c r="J30" s="6"/>
-      <c r="K30" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L30" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M30" s="22" t="s">
-        <v>205</v>
+      <c r="K30" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>4</v>
@@ -3343,14 +3311,14 @@
       <c r="J31" s="6">
         <v>37</v>
       </c>
-      <c r="K31" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L31" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M31" s="22" t="s">
-        <v>205</v>
+      <c r="K31" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N31" s="7"/>
       <c r="O31" s="12"/>
@@ -3384,14 +3352,14 @@
       <c r="J32" s="6">
         <v>159</v>
       </c>
-      <c r="K32" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M32" s="22" t="s">
-        <v>205</v>
+      <c r="K32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N32" s="7"/>
       <c r="O32" s="7"/>
@@ -3425,14 +3393,14 @@
       <c r="J33" s="6">
         <v>159</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M33" s="22" t="s">
-        <v>205</v>
+      <c r="K33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N33" s="7"/>
       <c r="O33" s="7"/>
@@ -3466,14 +3434,14 @@
       <c r="J34" s="6">
         <v>159</v>
       </c>
-      <c r="K34" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M34" s="22" t="s">
-        <v>205</v>
+      <c r="K34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N34" s="7"/>
       <c r="O34" s="7"/>
@@ -3507,14 +3475,14 @@
       <c r="J35" s="6">
         <v>159</v>
       </c>
-      <c r="K35" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M35" s="22" t="s">
-        <v>205</v>
+      <c r="K35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N35" s="7"/>
       <c r="O35" s="9"/>
@@ -3542,22 +3510,22 @@
         <v>6</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="K36" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L36" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M36" s="22" t="s">
-        <v>205</v>
+        <v>311</v>
+      </c>
+      <c r="K36" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="7"/>
@@ -3585,22 +3553,22 @@
         <v>6</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="K37" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L37" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M37" s="22" t="s">
-        <v>205</v>
+        <v>311</v>
+      </c>
+      <c r="K37" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="12"/>
@@ -3632,20 +3600,20 @@
         <v>9</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K38" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L38" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M38" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K38" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N38" s="7"/>
       <c r="O38" s="7" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" spans="1:15" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -3671,22 +3639,22 @@
         <v>6</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K39" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L39" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M39" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K39" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="7" t="s">
@@ -3695,10 +3663,10 @@
     </row>
     <row r="40" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>4</v>
@@ -3722,24 +3690,24 @@
       <c r="J40" s="6">
         <v>111</v>
       </c>
-      <c r="K40" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L40" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M40" s="22" t="s">
-        <v>205</v>
+      <c r="K40" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N40" s="7"/>
       <c r="O40" s="9"/>
     </row>
     <row r="41" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>4</v>
@@ -3763,14 +3731,14 @@
       <c r="J41" s="6">
         <v>111</v>
       </c>
-      <c r="K41" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L41" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M41" s="22" t="s">
-        <v>205</v>
+      <c r="K41" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N41" s="7"/>
       <c r="O41" s="9"/>
@@ -3802,26 +3770,26 @@
         <v>9</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L42" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M42" s="22" t="s">
-        <v>205</v>
+        <v>311</v>
+      </c>
+      <c r="K42" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N42" s="7"/>
       <c r="O42" s="9"/>
     </row>
     <row r="43" spans="1:15" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>4</v>
@@ -3843,16 +3811,16 @@
         <v>9</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L43" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M43" s="22" t="s">
-        <v>205</v>
+        <v>311</v>
+      </c>
+      <c r="K43" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N43" s="7"/>
       <c r="O43" s="9"/>
@@ -3862,7 +3830,7 @@
         <v>69</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>4</v>
@@ -3884,24 +3852,24 @@
         <v>9</v>
       </c>
       <c r="J44" s="6"/>
-      <c r="K44" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L44" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M44" s="22" t="s">
-        <v>205</v>
+      <c r="K44" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N44" s="7"/>
       <c r="O44" s="9"/>
     </row>
     <row r="45" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>4</v>
@@ -3916,21 +3884,21 @@
         <v>0</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J45" s="6"/>
-      <c r="K45" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L45" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M45" s="22" t="s">
-        <v>205</v>
+      <c r="K45" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N45" s="7"/>
       <c r="O45" s="9"/>
@@ -3940,7 +3908,7 @@
         <v>84</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>4</v>
@@ -3962,26 +3930,26 @@
         <v>9</v>
       </c>
       <c r="J46" s="6"/>
-      <c r="K46" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L46" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M46" s="22" t="s">
-        <v>205</v>
+      <c r="K46" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N46" s="7" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="O46" s="9"/>
     </row>
     <row r="47" spans="1:15" s="8" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>4</v>
@@ -3996,35 +3964,35 @@
         <v>0</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J47" s="6"/>
-      <c r="K47" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L47" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M47" s="22" t="s">
-        <v>205</v>
+      <c r="K47" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N47" s="7" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>4</v>
@@ -4046,14 +4014,14 @@
         <v>7</v>
       </c>
       <c r="J48" s="6"/>
-      <c r="K48" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L48" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M48" s="22" t="s">
-        <v>205</v>
+      <c r="K48" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N48" s="7"/>
       <c r="O48" s="7" t="s">
@@ -4079,7 +4047,7 @@
       <c r="F49" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G49" s="38" t="s">
+      <c r="G49" s="33" t="s">
         <v>88</v>
       </c>
       <c r="H49" s="7"/>
@@ -4087,17 +4055,17 @@
         <v>9</v>
       </c>
       <c r="J49" s="6"/>
-      <c r="K49" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L49" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="O49" s="38" t="s">
-        <v>445</v>
+      <c r="K49" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" s="33" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="45" x14ac:dyDescent="0.25">
@@ -4105,7 +4073,7 @@
         <v>66</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>13</v>
@@ -4123,32 +4091,32 @@
         <v>6</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="K50" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L50" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M50" s="22" t="s">
-        <v>205</v>
+        <v>308</v>
+      </c>
+      <c r="K50" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="12"/>
     </row>
     <row r="51" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>13</v>
@@ -4163,78 +4131,78 @@
         <v>0</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="K51" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L51" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M51" s="22" t="s">
-        <v>205</v>
+        <v>308</v>
+      </c>
+      <c r="K51" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="12"/>
     </row>
     <row r="52" spans="1:15" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="B52" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="C52" s="33" t="s">
+      <c r="A52" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="34" t="b">
+      <c r="D52" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="29" t="b">
         <v>0</v>
       </c>
       <c r="F52" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G52" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H52" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="I52" s="33" t="s">
+      <c r="G52" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H52" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="I52" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="K52" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L52" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M52" s="22" t="s">
-        <v>205</v>
+        <v>308</v>
+      </c>
+      <c r="K52" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N52" s="13"/>
       <c r="O52" s="7"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>4</v>
@@ -4256,14 +4224,14 @@
         <v>7</v>
       </c>
       <c r="J53" s="6"/>
-      <c r="K53" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L53" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M53" s="22" t="s">
-        <v>205</v>
+      <c r="K53" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N53" s="7"/>
       <c r="O53" s="7" t="s">
@@ -4272,10 +4240,10 @@
     </row>
     <row r="54" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>4</v>
@@ -4290,21 +4258,21 @@
         <v>0</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J54" s="6"/>
-      <c r="K54" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L54" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M54" s="22" t="s">
-        <v>205</v>
+      <c r="K54" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N54" s="7"/>
       <c r="O54" s="7" t="s">
@@ -4316,7 +4284,7 @@
         <v>37</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>4</v>
@@ -4331,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="7" t="s">
@@ -4340,14 +4308,14 @@
       <c r="J55" s="6">
         <v>108</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M55" s="22" t="s">
-        <v>205</v>
+      <c r="K55" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M55" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N55" s="7"/>
       <c r="O55" s="9"/>
@@ -4357,7 +4325,7 @@
         <v>38</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>4</v>
@@ -4372,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H56" s="7"/>
       <c r="I56" s="7" t="s">
@@ -4381,55 +4349,55 @@
       <c r="J56" s="6">
         <v>108</v>
       </c>
-      <c r="K56" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M56" s="22" t="s">
-        <v>205</v>
+      <c r="K56" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M56" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N56" s="7"/>
       <c r="O56" s="9"/>
     </row>
     <row r="57" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="32" t="s">
+      <c r="A57" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B57" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="C57" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="34" t="b">
+      <c r="B57" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F57" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G57" s="33" t="s">
-        <v>428</v>
+      <c r="G57" s="28" t="s">
+        <v>422</v>
       </c>
       <c r="H57" s="20"/>
-      <c r="I57" s="33" t="s">
+      <c r="I57" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J57" s="6">
         <v>108</v>
       </c>
-      <c r="K57" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M57" s="22" t="s">
-        <v>205</v>
+      <c r="K57" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M57" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N57" s="26"/>
       <c r="O57" s="7"/>
@@ -4439,7 +4407,7 @@
         <v>76</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>4</v>
@@ -4463,23 +4431,23 @@
       <c r="J58" s="6">
         <v>108</v>
       </c>
-      <c r="K58" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L58" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M58" s="22" t="s">
-        <v>205</v>
+      <c r="K58" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N58" s="7"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>4</v>
@@ -4503,54 +4471,54 @@
       <c r="J59" s="6">
         <v>108</v>
       </c>
-      <c r="K59" s="6" t="s">
+      <c r="K59" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" s="7"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="B60" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="L59" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M59" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N59" s="7"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="32" t="s">
-        <v>429</v>
-      </c>
-      <c r="B60" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="C60" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" s="34" t="b">
+      <c r="C60" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F60" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G60" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33" t="s">
+      <c r="G60" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J60" s="6">
         <v>108</v>
       </c>
-      <c r="K60" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L60" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M60" s="22" t="s">
-        <v>205</v>
+      <c r="K60" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N60" s="26"/>
       <c r="O60" s="7"/>
@@ -4584,14 +4552,14 @@
       <c r="J61" s="6">
         <v>66</v>
       </c>
-      <c r="K61" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L61" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M61" s="22" t="s">
-        <v>205</v>
+      <c r="K61" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N61" s="4"/>
     </row>
@@ -4600,7 +4568,7 @@
         <v>80</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>4</v>
@@ -4622,16 +4590,16 @@
         <v>9</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L62" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M62" s="22" t="s">
-        <v>205</v>
+        <v>254</v>
+      </c>
+      <c r="K62" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
@@ -4659,7 +4627,7 @@
         <v>88</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I63" s="7" t="s">
         <v>9</v>
@@ -4667,14 +4635,14 @@
       <c r="J63" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="K63" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L63" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M63" s="22" t="s">
-        <v>205</v>
+      <c r="K63" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N63" s="4"/>
       <c r="O63" s="7" t="s">
@@ -4708,14 +4676,14 @@
         <v>9</v>
       </c>
       <c r="J64" s="6"/>
-      <c r="K64" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L64" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M64" s="22" t="s">
-        <v>205</v>
+      <c r="K64" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="12"/>
@@ -4743,22 +4711,22 @@
         <v>88</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="K65" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L65" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M65" s="22" t="s">
-        <v>205</v>
+        <v>305</v>
+      </c>
+      <c r="K65" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N65" s="4"/>
       <c r="O65" s="12"/>
@@ -4768,7 +4736,7 @@
         <v>95</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>4</v>
@@ -4792,14 +4760,14 @@
       <c r="J66" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K66" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L66" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M66" s="22" t="s">
-        <v>205</v>
+      <c r="K66" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
@@ -4833,14 +4801,14 @@
       <c r="J67" s="6">
         <v>15</v>
       </c>
-      <c r="K67" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L67" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M67" s="22" t="s">
-        <v>205</v>
+      <c r="K67" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N67" s="7"/>
     </row>
@@ -4873,23 +4841,23 @@
       <c r="J68" s="6">
         <v>7</v>
       </c>
-      <c r="K68" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L68" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M68" s="22" t="s">
-        <v>205</v>
+      <c r="K68" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N68" s="4"/>
     </row>
     <row r="69" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>4</v>
@@ -4911,19 +4879,19 @@
         <v>9</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="K69" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L69" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M69" s="22" t="s">
-        <v>205</v>
+        <v>302</v>
+      </c>
+      <c r="K69" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="45" x14ac:dyDescent="0.25">
@@ -4949,22 +4917,22 @@
         <v>6</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="K70" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L70" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M70" s="22" t="s">
-        <v>205</v>
+        <v>306</v>
+      </c>
+      <c r="K70" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N70" s="4"/>
       <c r="O70" s="12"/>
@@ -4996,22 +4964,22 @@
         <v>9</v>
       </c>
       <c r="J71" s="6"/>
-      <c r="K71" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L71" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M71" s="6" t="s">
-        <v>206</v>
+      <c r="K71" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" s="6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>4</v>
@@ -5035,14 +5003,14 @@
       <c r="J72" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="K72" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L72" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M72" s="22" t="s">
-        <v>205</v>
+      <c r="K72" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N72" s="7"/>
       <c r="O72" s="7"/>
@@ -5076,14 +5044,14 @@
       <c r="J73" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K73" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L73" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M73" s="22" t="s">
-        <v>205</v>
+      <c r="K73" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N73" s="7"/>
     </row>
@@ -5116,14 +5084,14 @@
       <c r="J74" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K74" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L74" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M74" s="22" t="s">
-        <v>205</v>
+      <c r="K74" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="O74" s="12"/>
     </row>
@@ -5156,14 +5124,14 @@
       <c r="J75" s="6">
         <v>629</v>
       </c>
-      <c r="K75" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L75" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M75" s="22" t="s">
-        <v>205</v>
+      <c r="K75" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N75" s="7"/>
       <c r="O75" s="7"/>
@@ -5195,16 +5163,16 @@
         <v>9</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="K76" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L76" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M76" s="22" t="s">
-        <v>205</v>
+        <v>300</v>
+      </c>
+      <c r="K76" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N76" s="7"/>
       <c r="O76" s="12"/>
@@ -5214,7 +5182,7 @@
         <v>116</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>4</v>
@@ -5238,17 +5206,17 @@
       <c r="J77" s="6">
         <v>15</v>
       </c>
-      <c r="K77" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L77" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M77" s="22" t="s">
-        <v>205</v>
+      <c r="K77" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="O77" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="75" x14ac:dyDescent="0.25">
@@ -5270,7 +5238,7 @@
       <c r="F78" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G78" s="38" t="s">
+      <c r="G78" s="33" t="s">
         <v>88</v>
       </c>
       <c r="H78" s="7"/>
@@ -5280,18 +5248,18 @@
       <c r="J78" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="K78" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L78" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M78" s="6" t="s">
-        <v>206</v>
+      <c r="K78" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="N78" s="7"/>
-      <c r="O78" s="38" t="s">
-        <v>446</v>
+      <c r="O78" s="33" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
@@ -5321,23 +5289,23 @@
         <v>9</v>
       </c>
       <c r="J79" s="6"/>
-      <c r="K79" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L79" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M79" s="22" t="s">
-        <v>205</v>
+      <c r="K79" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N79" s="7"/>
     </row>
     <row r="80" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>153</v>
@@ -5351,38 +5319,38 @@
       <c r="F80" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G80" s="38" t="s">
+      <c r="G80" s="33" t="s">
         <v>88</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I80" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="K80" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L80" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M80" s="22" t="s">
-        <v>205</v>
+        <v>315</v>
+      </c>
+      <c r="K80" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N80" s="4"/>
-      <c r="O80" s="39" t="s">
-        <v>447</v>
+      <c r="O80" s="34" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>4</v>
@@ -5404,23 +5372,23 @@
         <v>9</v>
       </c>
       <c r="J81" s="6"/>
-      <c r="K81" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L81" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M81" s="22" t="s">
-        <v>205</v>
+      <c r="K81" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N81" s="7"/>
     </row>
     <row r="82" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>4</v>
@@ -5434,7 +5402,7 @@
       <c r="F82" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G82" s="38" t="s">
+      <c r="G82" s="33" t="s">
         <v>88</v>
       </c>
       <c r="H82" s="7"/>
@@ -5444,18 +5412,18 @@
       <c r="J82" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K82" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L82" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M82" s="22" t="s">
-        <v>205</v>
+      <c r="K82" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L82" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N82" s="7"/>
-      <c r="O82" s="38" t="s">
-        <v>445</v>
+      <c r="O82" s="33" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
@@ -5463,7 +5431,7 @@
         <v>124</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>4</v>
@@ -5485,16 +5453,16 @@
         <v>9</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="K83" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L83" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M83" s="22" t="s">
-        <v>205</v>
+        <v>245</v>
+      </c>
+      <c r="K83" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N83" s="4"/>
       <c r="O83" s="12"/>
@@ -5504,7 +5472,7 @@
         <v>85</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>13</v>
@@ -5522,32 +5490,32 @@
         <v>6</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I84" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="K84" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L84" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M84" s="22" t="s">
-        <v>205</v>
+        <v>310</v>
+      </c>
+      <c r="K84" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N84" s="4"/>
       <c r="O84" s="12"/>
     </row>
     <row r="85" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>13</v>
@@ -5562,68 +5530,68 @@
         <v>0</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="K85" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L85" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M85" s="22" t="s">
-        <v>205</v>
+        <v>310</v>
+      </c>
+      <c r="K85" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N85" s="4"/>
       <c r="O85" s="12"/>
     </row>
     <row r="86" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A86" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="B86" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="C86" s="33" t="s">
+      <c r="A86" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="B86" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C86" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D86" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="34" t="b">
+      <c r="D86" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="29" t="b">
         <v>0</v>
       </c>
       <c r="F86" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G86" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H86" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="I86" s="33" t="s">
+      <c r="G86" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H86" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="I86" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="K86" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L86" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M86" s="22" t="s">
-        <v>205</v>
+        <v>310</v>
+      </c>
+      <c r="K86" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N86" s="13"/>
       <c r="O86" s="7"/>
@@ -5633,7 +5601,7 @@
         <v>117</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>13</v>
@@ -5651,22 +5619,22 @@
         <v>6</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K87" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L87" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M87" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K87" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N87" s="4"/>
       <c r="O87" s="7" t="s">
@@ -5678,7 +5646,7 @@
         <v>120</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>13</v>
@@ -5696,22 +5664,22 @@
         <v>6</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K88" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L88" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M88" s="22" t="s">
-        <v>205</v>
+        <v>171</v>
+      </c>
+      <c r="K88" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N88" s="4"/>
       <c r="O88" s="7" t="s">
@@ -5720,10 +5688,10 @@
     </row>
     <row r="89" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>4</v>
@@ -5745,26 +5713,26 @@
         <v>7</v>
       </c>
       <c r="J89" s="6"/>
-      <c r="K89" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L89" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M89" s="22" t="s">
-        <v>205</v>
+      <c r="K89" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L89" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N89" s="7"/>
       <c r="O89" s="7" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>4</v>
@@ -5786,24 +5754,24 @@
         <v>9</v>
       </c>
       <c r="J90" s="6"/>
-      <c r="K90" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L90" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M90" s="22" t="s">
-        <v>205</v>
+      <c r="K90" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L90" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N90" s="7"/>
       <c r="O90" s="7"/>
     </row>
     <row r="91" spans="1:15" s="8" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>4</v>
@@ -5825,14 +5793,14 @@
         <v>9</v>
       </c>
       <c r="J91" s="6"/>
-      <c r="K91" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L91" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M91" s="22" t="s">
-        <v>205</v>
+      <c r="K91" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L91" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N91" s="7"/>
       <c r="O91" s="9"/>
@@ -5842,7 +5810,7 @@
         <v>40</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>4</v>
@@ -5857,23 +5825,23 @@
         <v>0</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H92" s="7"/>
       <c r="I92" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="K92" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L92" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M92" s="22" t="s">
-        <v>205</v>
+        <v>243</v>
+      </c>
+      <c r="K92" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N92" s="7" t="s">
         <v>41</v>
@@ -5884,10 +5852,10 @@
     </row>
     <row r="93" spans="1:15" s="8" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>4</v>
@@ -5911,24 +5879,24 @@
       <c r="J93" s="6">
         <v>98</v>
       </c>
-      <c r="K93" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L93" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M93" s="22" t="s">
-        <v>205</v>
+      <c r="K93" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L93" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N93" s="7"/>
       <c r="O93" s="12"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>4</v>
@@ -5952,14 +5920,14 @@
       <c r="J94" s="6">
         <v>45</v>
       </c>
-      <c r="K94" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L94" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M94" s="22" t="s">
-        <v>205</v>
+      <c r="K94" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N94" s="4"/>
       <c r="O94" s="12"/>
@@ -5993,23 +5961,23 @@
       <c r="J95" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K95" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L95" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M95" s="22" t="s">
-        <v>205</v>
+      <c r="K95" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L95" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N95" s="7"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>4</v>
@@ -6033,24 +6001,24 @@
       <c r="J96" s="6">
         <v>52</v>
       </c>
-      <c r="K96" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L96" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M96" s="22" t="s">
-        <v>205</v>
+      <c r="K96" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N96" s="4"/>
       <c r="O96" s="12"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>4</v>
@@ -6065,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H97" s="7"/>
       <c r="I97" s="7" t="s">
@@ -6074,65 +6042,65 @@
       <c r="J97" s="6">
         <v>52</v>
       </c>
-      <c r="K97" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L97" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M97" s="22" t="s">
-        <v>205</v>
+      <c r="K97" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N97" s="4"/>
       <c r="O97" s="12"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A98" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="B98" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="C98" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D98" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E98" s="34" t="b">
+      <c r="A98" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="B98" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="C98" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F98" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G98" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H98" s="33"/>
-      <c r="I98" s="33" t="s">
+      <c r="G98" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H98" s="28"/>
+      <c r="I98" s="28" t="s">
         <v>9</v>
       </c>
       <c r="J98" s="6">
         <v>52</v>
       </c>
-      <c r="K98" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L98" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M98" s="22" t="s">
-        <v>205</v>
+      <c r="K98" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N98" s="13"/>
       <c r="O98" s="7"/>
     </row>
     <row r="99" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C99" s="7" t="s">
         <v>4</v>
@@ -6156,24 +6124,24 @@
       <c r="J99" s="6">
         <v>15</v>
       </c>
-      <c r="K99" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L99" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M99" s="22" t="s">
-        <v>205</v>
+      <c r="K99" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N99" s="4"/>
       <c r="O99" s="12"/>
     </row>
     <row r="100" spans="1:15" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>4</v>
@@ -6197,24 +6165,24 @@
       <c r="J100" s="6">
         <v>67</v>
       </c>
-      <c r="K100" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L100" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M100" s="22" t="s">
-        <v>205</v>
+      <c r="K100" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N100" s="4"/>
       <c r="O100" s="12"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>4</v>
@@ -6229,7 +6197,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H101" s="7"/>
       <c r="I101" s="7" t="s">
@@ -6238,55 +6206,55 @@
       <c r="J101" s="6">
         <v>67</v>
       </c>
-      <c r="K101" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L101" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M101" s="22" t="s">
-        <v>205</v>
+      <c r="K101" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N101" s="4"/>
       <c r="O101" s="12"/>
     </row>
     <row r="102" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="32" t="s">
-        <v>346</v>
-      </c>
-      <c r="B102" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="C102" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D102" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E102" s="34" t="b">
+      <c r="A102" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="B102" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="C102" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D102" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F102" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G102" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H102" s="33"/>
-      <c r="I102" s="33" t="s">
+      <c r="G102" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H102" s="28"/>
+      <c r="I102" s="28" t="s">
         <v>9</v>
       </c>
       <c r="J102" s="6">
         <v>67</v>
       </c>
-      <c r="K102" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L102" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M102" s="22" t="s">
-        <v>205</v>
+      <c r="K102" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M102" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N102" s="13"/>
       <c r="O102" s="7"/>
@@ -6296,7 +6264,7 @@
         <v>72</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>4</v>
@@ -6318,14 +6286,14 @@
         <v>7</v>
       </c>
       <c r="J103" s="6"/>
-      <c r="K103" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L103" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M103" s="22" t="s">
-        <v>205</v>
+      <c r="K103" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L103" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M103" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N103" s="7"/>
       <c r="O103" s="7" t="s">
@@ -6334,10 +6302,10 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>4</v>
@@ -6352,21 +6320,21 @@
         <v>0</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H104" s="7"/>
       <c r="I104" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J104" s="6"/>
-      <c r="K104" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L104" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M104" s="22" t="s">
-        <v>205</v>
+      <c r="K104" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L104" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N104" s="7"/>
       <c r="O104" s="7" t="s">
@@ -6378,7 +6346,7 @@
         <v>74</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>4</v>
@@ -6400,14 +6368,14 @@
         <v>7</v>
       </c>
       <c r="J105" s="6"/>
-      <c r="K105" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L105" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M105" s="22" t="s">
-        <v>205</v>
+      <c r="K105" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L105" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N105" s="7"/>
       <c r="O105" s="7" t="s">
@@ -6416,10 +6384,10 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>4</v>
@@ -6434,21 +6402,21 @@
         <v>0</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H106" s="7"/>
       <c r="I106" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J106" s="6"/>
-      <c r="K106" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L106" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M106" s="22" t="s">
-        <v>205</v>
+      <c r="K106" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L106" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M106" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N106" s="7"/>
       <c r="O106" s="7" t="s">
@@ -6460,7 +6428,7 @@
         <v>75</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>4</v>
@@ -6482,14 +6450,14 @@
         <v>7</v>
       </c>
       <c r="J107" s="6"/>
-      <c r="K107" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L107" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M107" s="22" t="s">
-        <v>205</v>
+      <c r="K107" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L107" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M107" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N107" s="7"/>
       <c r="O107" s="7" t="s">
@@ -6498,10 +6466,10 @@
     </row>
     <row r="108" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>4</v>
@@ -6516,21 +6484,21 @@
         <v>0</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H108" s="7"/>
       <c r="I108" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J108" s="6"/>
-      <c r="K108" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L108" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M108" s="22" t="s">
-        <v>205</v>
+      <c r="K108" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L108" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M108" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N108" s="7"/>
       <c r="O108" s="7" t="s">
@@ -6567,13 +6535,13 @@
         <v>133</v>
       </c>
       <c r="K109" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L109" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M109" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
+      </c>
+      <c r="L109" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M109" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="N109" s="7"/>
       <c r="O109" s="7" t="s">
@@ -6599,7 +6567,7 @@
       <c r="F110" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G110" s="38" t="s">
+      <c r="G110" s="33" t="s">
         <v>88</v>
       </c>
       <c r="H110" s="7"/>
@@ -6607,28 +6575,28 @@
         <v>9</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L110" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M110" s="22" t="s">
-        <v>205</v>
+        <v>301</v>
+      </c>
+      <c r="K110" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L110" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M110" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N110" s="7"/>
-      <c r="O110" s="38" t="s">
-        <v>449</v>
+      <c r="O110" s="33" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>4</v>
@@ -6650,24 +6618,24 @@
         <v>9</v>
       </c>
       <c r="J111" s="6"/>
-      <c r="K111" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L111" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M111" s="22" t="s">
-        <v>205</v>
+      <c r="K111" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L111" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M111" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N111" s="7"/>
       <c r="O111" s="7"/>
     </row>
     <row r="112" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>4</v>
@@ -6689,20 +6657,20 @@
         <v>9</v>
       </c>
       <c r="J112" s="6"/>
-      <c r="K112" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L112" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M112" s="22" t="s">
-        <v>205</v>
+      <c r="K112" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L112" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N112" s="7" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="O112" s="7" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -6732,24 +6700,24 @@
         <v>7</v>
       </c>
       <c r="J113" s="6"/>
-      <c r="K113" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L113" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M113" s="22" t="s">
-        <v>205</v>
+      <c r="K113" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L113" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M113" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N113" s="7"/>
       <c r="O113" s="7"/>
     </row>
     <row r="114" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B114" s="24" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C114" s="20" t="s">
         <v>4</v>
@@ -6771,18 +6739,18 @@
         <v>7</v>
       </c>
       <c r="J114" s="21"/>
-      <c r="K114" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L114" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M114" s="22" t="s">
-        <v>205</v>
+      <c r="K114" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L114" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N114" s="7"/>
       <c r="O114" s="20" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -6814,24 +6782,24 @@
       <c r="J115" s="6">
         <v>28</v>
       </c>
-      <c r="K115" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L115" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M115" s="22" t="s">
-        <v>205</v>
+      <c r="K115" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L115" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M115" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N115" s="7"/>
       <c r="O115" s="7"/>
     </row>
     <row r="116" spans="1:15" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>4</v>
@@ -6853,24 +6821,24 @@
         <v>9</v>
       </c>
       <c r="J116" s="6"/>
-      <c r="K116" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L116" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M116" s="22" t="s">
-        <v>205</v>
+      <c r="K116" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L116" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M116" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N116" s="7"/>
       <c r="O116" s="7"/>
     </row>
     <row r="117" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>4</v>
@@ -6894,24 +6862,24 @@
       <c r="J117" s="6">
         <v>106</v>
       </c>
-      <c r="K117" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L117" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M117" s="22" t="s">
-        <v>205</v>
+      <c r="K117" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L117" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M117" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="12"/>
     </row>
     <row r="118" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="14" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>4</v>
@@ -6935,24 +6903,24 @@
       <c r="J118" s="6">
         <v>105</v>
       </c>
-      <c r="K118" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L118" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M118" s="22" t="s">
-        <v>205</v>
+      <c r="K118" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L118" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="12"/>
     </row>
     <row r="119" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="14" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>4</v>
@@ -6967,74 +6935,74 @@
         <v>0</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H119" s="7"/>
       <c r="I119" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K119" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L119" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M119" s="22" t="s">
-        <v>205</v>
+        <v>307</v>
+      </c>
+      <c r="K119" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L119" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M119" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N119" s="7"/>
       <c r="O119" s="7"/>
     </row>
     <row r="120" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="32" t="s">
-        <v>421</v>
-      </c>
-      <c r="B120" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="C120" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D120" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E120" s="34" t="b">
+      <c r="A120" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="B120" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="C120" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F120" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G120" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H120" s="33"/>
-      <c r="I120" s="33" t="s">
+      <c r="G120" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H120" s="28"/>
+      <c r="I120" s="28" t="s">
         <v>9</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K120" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L120" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M120" s="22" t="s">
-        <v>205</v>
+        <v>307</v>
+      </c>
+      <c r="K120" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L120" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M120" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N120" s="26"/>
       <c r="O120" s="7"/>
     </row>
     <row r="121" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="14" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>4</v>
@@ -7056,26 +7024,26 @@
         <v>7</v>
       </c>
       <c r="J121" s="6"/>
-      <c r="K121" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L121" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M121" s="22" t="s">
-        <v>205</v>
+      <c r="K121" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L121" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N121" s="7"/>
       <c r="O121" s="7" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="122" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>4</v>
@@ -7099,18 +7067,18 @@
       <c r="J122" s="6">
         <v>10</v>
       </c>
-      <c r="K122" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L122" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M122" s="22" t="s">
-        <v>205</v>
+      <c r="K122" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L122" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N122" s="7"/>
       <c r="O122" s="7" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="123" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -7118,7 +7086,7 @@
         <v>138</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>13</v>
@@ -7136,32 +7104,32 @@
         <v>6</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I123" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J123" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="K123" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L123" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M123" s="22" t="s">
-        <v>205</v>
+        <v>309</v>
+      </c>
+      <c r="K123" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L123" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N123" s="4"/>
       <c r="O123" s="12"/>
     </row>
     <row r="124" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>13</v>
@@ -7176,78 +7144,78 @@
         <v>0</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="I124" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="K124" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L124" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M124" s="22" t="s">
-        <v>205</v>
+        <v>309</v>
+      </c>
+      <c r="K124" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L124" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N124" s="4"/>
       <c r="O124" s="12"/>
     </row>
     <row r="125" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="B125" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="C125" s="33" t="s">
+      <c r="A125" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="B125" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="C125" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D125" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E125" s="34" t="b">
+      <c r="D125" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="29" t="b">
         <v>0</v>
       </c>
       <c r="F125" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G125" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H125" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="I125" s="33" t="s">
+      <c r="G125" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H125" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="I125" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="K125" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L125" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M125" s="22" t="s">
-        <v>205</v>
+        <v>309</v>
+      </c>
+      <c r="K125" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L125" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N125" s="13"/>
       <c r="O125" s="7"/>
     </row>
     <row r="126" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C126" s="7" t="s">
         <v>4</v>
@@ -7269,28 +7237,28 @@
         <v>7</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="K126" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L126" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M126" s="22" t="s">
-        <v>205</v>
+        <v>402</v>
+      </c>
+      <c r="K126" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L126" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M126" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N126" s="7"/>
       <c r="O126" s="7" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
     </row>
     <row r="127" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B127" s="24" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C127" s="20" t="s">
         <v>4</v>
@@ -7311,19 +7279,19 @@
       <c r="I127" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="J127" s="37"/>
-      <c r="K127" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L127" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M127" s="22" t="s">
-        <v>205</v>
+      <c r="J127" s="32"/>
+      <c r="K127" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L127" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M127" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N127" s="7"/>
       <c r="O127" s="20" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="128" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -7331,7 +7299,7 @@
         <v>156</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C128" s="7" t="s">
         <v>153</v>
@@ -7349,7 +7317,7 @@
         <v>6</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>7</v>
@@ -7357,24 +7325,24 @@
       <c r="J128" s="6">
         <v>127</v>
       </c>
-      <c r="K128" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L128" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M128" s="22" t="s">
-        <v>205</v>
+      <c r="K128" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L128" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M128" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N128" s="4"/>
       <c r="O128" s="12"/>
     </row>
     <row r="129" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C129" s="7" t="s">
         <v>153</v>
@@ -7389,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H129" s="7" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>7</v>
@@ -7400,57 +7368,57 @@
       <c r="J129" s="6">
         <v>127</v>
       </c>
-      <c r="K129" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L129" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M129" s="22" t="s">
-        <v>205</v>
+      <c r="K129" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L129" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M129" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N129" s="4"/>
       <c r="O129" s="12"/>
     </row>
     <row r="130" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="32" t="s">
-        <v>422</v>
-      </c>
-      <c r="B130" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="C130" s="33" t="s">
+      <c r="A130" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="B130" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C130" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="D130" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E130" s="34" t="b">
+      <c r="D130" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E130" s="29" t="b">
         <v>0</v>
       </c>
       <c r="F130" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G130" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H130" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="I130" s="33" t="s">
+      <c r="G130" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H130" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="I130" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J130" s="6">
         <v>127</v>
       </c>
-      <c r="K130" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L130" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M130" s="22" t="s">
-        <v>205</v>
+      <c r="K130" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L130" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M130" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N130" s="13"/>
       <c r="O130" s="12"/>
@@ -7478,22 +7446,22 @@
         <v>6</v>
       </c>
       <c r="H131" s="7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J131" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="K131" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L131" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M131" s="22" t="s">
-        <v>205</v>
+        <v>252</v>
+      </c>
+      <c r="K131" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L131" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M131" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N131" s="4"/>
       <c r="O131" s="7"/>
@@ -7521,7 +7489,7 @@
         <v>6</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>7</v>
@@ -7529,23 +7497,23 @@
       <c r="J132" s="6">
         <v>49</v>
       </c>
-      <c r="K132" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L132" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M132" s="22" t="s">
-        <v>205</v>
+      <c r="K132" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L132" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M132" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N132" s="4"/>
       <c r="O132" s="7" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:15" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B133" s="15" t="s">
         <v>3</v>
@@ -7570,24 +7538,24 @@
         <v>7</v>
       </c>
       <c r="J133" s="6"/>
-      <c r="K133" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L133" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M133" s="22" t="s">
-        <v>205</v>
+      <c r="K133" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L133" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M133" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N133" s="7"/>
       <c r="O133" s="7"/>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B134" s="23" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>4</v>
@@ -7611,24 +7579,24 @@
       <c r="J134" s="6">
         <v>110</v>
       </c>
-      <c r="K134" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L134" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M134" s="22" t="s">
-        <v>205</v>
+      <c r="K134" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L134" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M134" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N134" s="4"/>
       <c r="O134" s="12"/>
     </row>
     <row r="135" spans="1:15" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="14" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B135" s="23" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>4</v>
@@ -7643,7 +7611,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H135" s="7"/>
       <c r="I135" s="7" t="s">
@@ -7652,65 +7620,65 @@
       <c r="J135" s="6">
         <v>110</v>
       </c>
-      <c r="K135" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L135" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M135" s="22" t="s">
-        <v>205</v>
+      <c r="K135" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L135" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M135" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N135" s="4"/>
       <c r="O135" s="12"/>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A136" s="32" t="s">
-        <v>347</v>
-      </c>
-      <c r="B136" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="C136" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D136" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E136" s="34" t="b">
+      <c r="A136" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="B136" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="C136" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D136" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E136" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F136" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G136" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H136" s="33"/>
-      <c r="I136" s="33" t="s">
+      <c r="G136" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H136" s="28"/>
+      <c r="I136" s="28" t="s">
         <v>9</v>
       </c>
       <c r="J136" s="6">
         <v>110</v>
       </c>
-      <c r="K136" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L136" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M136" s="22" t="s">
-        <v>205</v>
+      <c r="K136" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L136" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M136" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N136" s="13"/>
       <c r="O136" s="7"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C137" s="7" t="s">
         <v>4</v>
@@ -7732,14 +7700,14 @@
         <v>9</v>
       </c>
       <c r="J137" s="6"/>
-      <c r="K137" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L137" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M137" s="22" t="s">
-        <v>205</v>
+      <c r="K137" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L137" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M137" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N137" s="7"/>
       <c r="O137" s="7"/>
@@ -7773,53 +7741,53 @@
       <c r="J138" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K138" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L138" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M138" s="22" t="s">
-        <v>205</v>
+      <c r="K138" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L138" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M138" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N138" s="4"/>
       <c r="O138" s="7"/>
     </row>
     <row r="139" spans="1:15" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="32" t="s">
-        <v>436</v>
-      </c>
-      <c r="B139" s="36" t="s">
-        <v>425</v>
-      </c>
-      <c r="C139" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D139" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E139" s="34" t="b">
+      <c r="A139" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="B139" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="C139" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D139" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E139" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F139" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G139" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H139" s="33"/>
-      <c r="I139" s="33" t="s">
+      <c r="G139" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H139" s="28"/>
+      <c r="I139" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J139" s="6"/>
-      <c r="K139" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L139" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M139" s="22" t="s">
-        <v>205</v>
+      <c r="K139" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L139" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M139" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N139" s="7"/>
       <c r="O139" s="7" t="s">
@@ -7828,10 +7796,10 @@
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="14" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C140" s="7" t="s">
         <v>4</v>
@@ -7855,20 +7823,20 @@
       <c r="J140" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K140" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L140" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M140" s="22" t="s">
-        <v>205</v>
+      <c r="K140" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L140" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M140" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N140" s="4"/>
     </row>
     <row r="141" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="14" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B141" s="16" t="s">
         <v>157</v>
@@ -7893,26 +7861,26 @@
         <v>7</v>
       </c>
       <c r="J141" s="6"/>
-      <c r="K141" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L141" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M141" s="22" t="s">
-        <v>205</v>
+      <c r="K141" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L141" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M141" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N141" s="4"/>
       <c r="O141" s="9" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="142" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C142" s="7" t="s">
         <v>4</v>
@@ -7936,26 +7904,26 @@
       <c r="J142" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K142" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L142" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M142" s="22" t="s">
-        <v>205</v>
+      <c r="K142" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L142" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M142" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N142" s="4"/>
       <c r="O142" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C143" s="7" t="s">
         <v>4</v>
@@ -7979,26 +7947,26 @@
       <c r="J143" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K143" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L143" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M143" s="22" t="s">
-        <v>205</v>
+      <c r="K143" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L143" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M143" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N143" s="4"/>
       <c r="O143" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C144" s="7" t="s">
         <v>4</v>
@@ -8022,18 +7990,18 @@
       <c r="J144" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K144" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L144" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M144" s="22" t="s">
-        <v>205</v>
+      <c r="K144" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L144" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M144" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N144" s="4"/>
       <c r="O144" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="145" spans="1:15" ht="60" x14ac:dyDescent="0.25">
@@ -8041,7 +8009,7 @@
         <v>8</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>4</v>
@@ -8065,18 +8033,18 @@
       <c r="J145" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K145" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L145" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M145" s="22" t="s">
-        <v>205</v>
+      <c r="K145" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L145" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M145" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N145" s="4"/>
       <c r="O145" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
@@ -8084,7 +8052,7 @@
         <v>77</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C146" s="7" t="s">
         <v>4</v>
@@ -8106,14 +8074,14 @@
         <v>7</v>
       </c>
       <c r="J146" s="6"/>
-      <c r="K146" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L146" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M146" s="22" t="s">
-        <v>205</v>
+      <c r="K146" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L146" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M146" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N146" s="7"/>
       <c r="O146" s="7" t="s">
@@ -8122,10 +8090,10 @@
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="14" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C147" s="7" t="s">
         <v>4</v>
@@ -8140,21 +8108,21 @@
         <v>0</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H147" s="7"/>
       <c r="I147" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J147" s="6"/>
-      <c r="K147" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L147" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M147" s="22" t="s">
-        <v>205</v>
+      <c r="K147" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L147" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M147" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N147" s="7"/>
       <c r="O147" s="7" t="s">
@@ -8162,40 +8130,40 @@
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A148" s="32" t="s">
-        <v>434</v>
-      </c>
-      <c r="B148" s="36" t="s">
-        <v>427</v>
-      </c>
-      <c r="C148" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D148" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E148" s="34" t="b">
+      <c r="A148" s="27" t="s">
+        <v>428</v>
+      </c>
+      <c r="B148" s="31" t="s">
+        <v>421</v>
+      </c>
+      <c r="C148" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D148" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E148" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F148" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G148" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H148" s="33"/>
-      <c r="I148" s="33" t="s">
+      <c r="G148" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H148" s="28"/>
+      <c r="I148" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J148" s="6"/>
-      <c r="K148" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L148" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M148" s="22" t="s">
-        <v>205</v>
+      <c r="K148" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L148" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M148" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N148" s="7"/>
       <c r="O148" s="7" t="s">
@@ -8231,14 +8199,14 @@
       <c r="J149" s="6">
         <v>111</v>
       </c>
-      <c r="K149" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L149" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M149" s="22" t="s">
-        <v>205</v>
+      <c r="K149" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L149" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M149" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N149" s="7"/>
     </row>
@@ -8271,67 +8239,65 @@
       <c r="J150" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="K150" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L150" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M150" s="6" t="s">
-        <v>206</v>
+      <c r="K150" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L150" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M150" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="N150" s="7"/>
       <c r="O150" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="151" spans="1:15" ht="105" x14ac:dyDescent="0.25">
-      <c r="A151" s="27" t="s">
-        <v>280</v>
-      </c>
-      <c r="B151" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="C151" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D151" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E151" s="10" t="b">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B151" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D151" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E151" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F151" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G151" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="H151" s="29"/>
-      <c r="I151" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J151" s="30"/>
-      <c r="K151" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="L151" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="M151" s="31" t="s">
-        <v>205</v>
+      <c r="G151" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H151" s="7"/>
+      <c r="I151" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J151" s="6"/>
+      <c r="K151" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L151" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M151" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N151" s="7"/>
-      <c r="O151" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O151" s="7"/>
+    </row>
+    <row r="152" spans="1:15" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="14" t="s">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>268</v>
+        <v>374</v>
       </c>
       <c r="C152" s="7" t="s">
         <v>4</v>
@@ -8350,109 +8316,111 @@
       </c>
       <c r="H152" s="7"/>
       <c r="I152" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J152" s="6"/>
-      <c r="K152" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L152" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M152" s="22" t="s">
-        <v>205</v>
+      <c r="K152" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L152" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M152" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N152" s="7"/>
-      <c r="O152" s="7"/>
-    </row>
-    <row r="153" spans="1:15" s="25" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A153" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B153" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="C153" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D153" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E153" s="10" t="b">
+      <c r="O152" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A153" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B153" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D153" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E153" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F153" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G153" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="H153" s="29"/>
-      <c r="I153" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J153" s="30"/>
-      <c r="K153" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="L153" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="M153" s="31" t="s">
-        <v>205</v>
+      <c r="G153" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="H153" s="7"/>
+      <c r="I153" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J153" s="6"/>
+      <c r="K153" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L153" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M153" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N153" s="7"/>
       <c r="O153" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A154" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B154" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="C154" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D154" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E154" s="4" t="b">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A154" s="27" t="s">
+        <v>429</v>
+      </c>
+      <c r="B154" s="31" t="s">
+        <v>420</v>
+      </c>
+      <c r="C154" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D154" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E154" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F154" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G154" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H154" s="7"/>
-      <c r="I154" s="7" t="s">
+      <c r="G154" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H154" s="28"/>
+      <c r="I154" s="28" t="s">
         <v>7</v>
       </c>
       <c r="J154" s="6"/>
-      <c r="K154" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L154" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M154" s="22" t="s">
-        <v>205</v>
+      <c r="K154" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L154" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M154" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N154" s="7"/>
       <c r="O154" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="14" t="s">
-        <v>368</v>
+        <v>279</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>387</v>
+        <v>278</v>
       </c>
       <c r="C155" s="7" t="s">
         <v>4</v>
@@ -8467,83 +8435,79 @@
         <v>0</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>178</v>
+        <v>6</v>
       </c>
       <c r="H155" s="7"/>
       <c r="I155" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J155" s="6"/>
+      <c r="K155" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L155" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M155" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N155" s="7"/>
+      <c r="O155" s="7"/>
+    </row>
+    <row r="156" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D156" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E156" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F156" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H156" s="7"/>
+      <c r="I156" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J155" s="6"/>
-      <c r="K155" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L155" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M155" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N155" s="7"/>
-      <c r="O155" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A156" s="32" t="s">
-        <v>435</v>
-      </c>
-      <c r="B156" s="36" t="s">
-        <v>426</v>
-      </c>
-      <c r="C156" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D156" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E156" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="F156" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G156" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H156" s="33"/>
-      <c r="I156" s="33" t="s">
-        <v>7</v>
-      </c>
       <c r="J156" s="6"/>
-      <c r="K156" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L156" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M156" s="22" t="s">
-        <v>205</v>
+      <c r="K156" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L156" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M156" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N156" s="7"/>
-      <c r="O156" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O156" s="12"/>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="B157" s="15" t="s">
-        <v>283</v>
+        <v>237</v>
+      </c>
+      <c r="B157" s="16" t="s">
+        <v>235</v>
       </c>
       <c r="C157" s="7" t="s">
         <v>4</v>
       </c>
       <c r="D157" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" s="4" t="b">
         <v>0</v>
@@ -8555,25 +8519,26 @@
       <c r="I157" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J157" s="6"/>
-      <c r="K157" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L157" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M157" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N157" s="7"/>
-      <c r="O157" s="7"/>
-    </row>
-    <row r="158" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J157" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K157" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L157" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M157" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N157" s="4"/>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="14" t="s">
-        <v>198</v>
+        <v>350</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>195</v>
+        <v>349</v>
       </c>
       <c r="C158" s="7" t="s">
         <v>4</v>
@@ -8592,67 +8557,70 @@
       </c>
       <c r="H158" s="7"/>
       <c r="I158" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J158" s="6"/>
-      <c r="K158" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L158" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M158" s="22" t="s">
-        <v>205</v>
+        <v>9</v>
+      </c>
+      <c r="J158" s="6">
+        <v>64</v>
+      </c>
+      <c r="K158" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L158" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M158" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="N158" s="7"/>
-      <c r="O158" s="12"/>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O158" s="7"/>
+    </row>
+    <row r="159" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="B159" s="16" t="s">
-        <v>238</v>
+        <v>351</v>
+      </c>
+      <c r="B159" s="23" t="s">
+        <v>290</v>
       </c>
       <c r="C159" s="7" t="s">
         <v>4</v>
       </c>
       <c r="D159" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="4" t="b">
         <v>0</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="H159" s="7"/>
       <c r="I159" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J159" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K159" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L159" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M159" s="22" t="s">
-        <v>205</v>
+      <c r="J159" s="6">
+        <v>143</v>
+      </c>
+      <c r="K159" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L159" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M159" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N159" s="4"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O159" s="12"/>
+    </row>
+    <row r="160" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>354</v>
+        <v>346</v>
+      </c>
+      <c r="B160" s="23" t="s">
+        <v>291</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>4</v>
@@ -8667,33 +8635,33 @@
         <v>0</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="H160" s="7"/>
       <c r="I160" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J160" s="6">
-        <v>64</v>
-      </c>
-      <c r="K160" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L160" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M160" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="N160" s="7"/>
-      <c r="O160" s="7"/>
-    </row>
-    <row r="161" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="K160" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L160" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M160" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N160" s="4"/>
+      <c r="O160" s="12"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="14" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C161" s="7" t="s">
         <v>4</v>
@@ -8708,33 +8676,33 @@
         <v>0</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H161" s="7"/>
       <c r="I161" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J161" s="6">
-        <v>143</v>
-      </c>
-      <c r="K161" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L161" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M161" s="22" t="s">
-        <v>205</v>
+        <v>112</v>
+      </c>
+      <c r="K161" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L161" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M161" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N161" s="4"/>
       <c r="O161" s="12"/>
     </row>
-    <row r="162" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="14" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B162" s="23" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>4</v>
@@ -8749,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H162" s="7"/>
       <c r="I162" s="7" t="s">
@@ -8758,24 +8726,24 @@
       <c r="J162" s="6">
         <v>112</v>
       </c>
-      <c r="K162" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L162" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M162" s="22" t="s">
-        <v>205</v>
+      <c r="K162" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L162" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M162" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N162" s="4"/>
       <c r="O162" s="12"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="B163" s="23" t="s">
-        <v>297</v>
+        <v>197</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>195</v>
       </c>
       <c r="C163" s="7" t="s">
         <v>4</v>
@@ -8790,74 +8758,74 @@
         <v>0</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H163" s="7"/>
       <c r="I163" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J163" s="6">
-        <v>112</v>
-      </c>
-      <c r="K163" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L163" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M163" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N163" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="J163" s="6"/>
+      <c r="K163" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L163" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M163" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N163" s="7"/>
       <c r="O163" s="12"/>
     </row>
-    <row r="164" spans="1:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="B164" s="23" t="s">
-        <v>298</v>
+        <v>238</v>
+      </c>
+      <c r="B164" s="16" t="s">
+        <v>236</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>4</v>
       </c>
       <c r="D164" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G164" s="7" t="s">
-        <v>178</v>
+      <c r="G164" s="33" t="s">
+        <v>176</v>
       </c>
       <c r="H164" s="7"/>
       <c r="I164" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J164" s="6">
-        <v>112</v>
-      </c>
-      <c r="K164" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L164" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M164" s="22" t="s">
-        <v>205</v>
+      <c r="J164" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K164" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L164" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M164" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N164" s="4"/>
-      <c r="O164" s="12"/>
-    </row>
-    <row r="165" spans="1:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O164" s="34" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" s="8" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="14" t="s">
-        <v>199</v>
+        <v>347</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>197</v>
+        <v>348</v>
       </c>
       <c r="C165" s="7" t="s">
         <v>4</v>
@@ -8872,441 +8840,359 @@
         <v>0</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H165" s="7"/>
       <c r="I165" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J165" s="6"/>
-      <c r="K165" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L165" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M165" s="22" t="s">
-        <v>205</v>
+        <v>9</v>
+      </c>
+      <c r="J165" s="6">
+        <v>64</v>
+      </c>
+      <c r="K165" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L165" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M165" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="N165" s="7"/>
-      <c r="O165" s="12"/>
-    </row>
-    <row r="166" spans="1:15" s="8" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A166" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="B166" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D166" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E166" s="4" t="b">
-        <v>0</v>
+      <c r="O165" s="7"/>
+    </row>
+    <row r="166" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="B166" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="C166" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D166" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E166" s="29" t="b">
+        <v>1</v>
       </c>
       <c r="F166" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G166" s="38" t="s">
+      <c r="G166" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="H166" s="7"/>
-      <c r="I166" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J166" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K166" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L166" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M166" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N166" s="4"/>
-      <c r="O166" s="39" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" s="8" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="C167" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D167" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E167" s="4" t="b">
+      <c r="H166" s="28"/>
+      <c r="I166" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J166" s="6">
+        <v>143</v>
+      </c>
+      <c r="K166" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L166" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M166" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N166" s="13"/>
+      <c r="O166" s="7"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="B167" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="C167" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D167" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E167" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F167" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G167" s="7" t="s">
+      <c r="G167" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="H167" s="7"/>
-      <c r="I167" s="7" t="s">
+      <c r="H167" s="28"/>
+      <c r="I167" s="28" t="s">
         <v>9</v>
       </c>
       <c r="J167" s="6">
-        <v>64</v>
-      </c>
-      <c r="K167" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L167" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M167" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="N167" s="7"/>
+        <v>112</v>
+      </c>
+      <c r="K167" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L167" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M167" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N167" s="13"/>
       <c r="O167" s="7"/>
     </row>
-    <row r="168" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="32" t="s">
-        <v>357</v>
-      </c>
-      <c r="B168" s="35" t="s">
-        <v>299</v>
-      </c>
-      <c r="C168" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D168" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E168" s="34" t="b">
+    <row r="168" spans="1:15" ht="73.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="27" t="s">
+        <v>425</v>
+      </c>
+      <c r="B168" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="C168" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D168" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E168" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F168" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G168" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H168" s="33"/>
-      <c r="I168" s="33" t="s">
+      <c r="G168" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H168" s="28"/>
+      <c r="I168" s="28" t="s">
         <v>9</v>
       </c>
       <c r="J168" s="6">
-        <v>143</v>
-      </c>
-      <c r="K168" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L168" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M168" s="22" t="s">
-        <v>205</v>
+        <v>112</v>
+      </c>
+      <c r="K168" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L168" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M168" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N168" s="13"/>
       <c r="O168" s="7"/>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A169" s="32" t="s">
-        <v>430</v>
-      </c>
-      <c r="B169" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="C169" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D169" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E169" s="34" t="b">
+      <c r="A169" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="B169" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="C169" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D169" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E169" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F169" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G169" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H169" s="33"/>
-      <c r="I169" s="33" t="s">
+      <c r="G169" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H169" s="28"/>
+      <c r="I169" s="28" t="s">
         <v>9</v>
       </c>
       <c r="J169" s="6">
         <v>112</v>
       </c>
-      <c r="K169" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L169" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M169" s="22" t="s">
-        <v>205</v>
+      <c r="K169" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L169" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M169" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N169" s="13"/>
       <c r="O169" s="7"/>
     </row>
-    <row r="170" spans="1:15" ht="73.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="32" t="s">
-        <v>431</v>
-      </c>
-      <c r="B170" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="C170" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D170" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E170" s="34" t="b">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="27" t="s">
+        <v>417</v>
+      </c>
+      <c r="B170" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C170" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D170" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E170" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F170" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G170" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H170" s="33"/>
-      <c r="I170" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J170" s="6">
-        <v>112</v>
-      </c>
-      <c r="K170" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L170" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M170" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N170" s="13"/>
+      <c r="G170" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H170" s="28"/>
+      <c r="I170" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="J170" s="6"/>
+      <c r="K170" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L170" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M170" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N170" s="26"/>
       <c r="O170" s="7"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A171" s="32" t="s">
-        <v>432</v>
-      </c>
-      <c r="B171" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="C171" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D171" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E171" s="34" t="b">
-        <v>1</v>
+    <row r="171" spans="1:15" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A171" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="B171" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="C171" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D171" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E171" s="29" t="b">
+        <v>0</v>
       </c>
       <c r="F171" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G171" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H171" s="33"/>
-      <c r="I171" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J171" s="6">
-        <v>112</v>
-      </c>
-      <c r="K171" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L171" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M171" s="22" t="s">
-        <v>205</v>
+      <c r="G171" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H171" s="28"/>
+      <c r="I171" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J171" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K171" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L171" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M171" s="22" t="b">
+        <v>0</v>
       </c>
       <c r="N171" s="13"/>
-      <c r="O171" s="7"/>
+      <c r="O171" s="7" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A172" s="32" t="s">
-        <v>423</v>
-      </c>
-      <c r="B172" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="C172" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D172" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E172" s="34" t="b">
+      <c r="A172" s="27" t="s">
+        <v>427</v>
+      </c>
+      <c r="B172" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="C172" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D172" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E172" s="29" t="b">
         <v>1</v>
       </c>
       <c r="F172" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G172" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H172" s="33"/>
-      <c r="I172" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="J172" s="6"/>
-      <c r="K172" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L172" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M172" s="22" t="s">
-        <v>205</v>
+      <c r="G172" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H172" s="28"/>
+      <c r="I172" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J172" s="6">
+        <v>64</v>
+      </c>
+      <c r="K172" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L172" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M172" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="N172" s="26"/>
       <c r="O172" s="7"/>
     </row>
-    <row r="173" spans="1:15" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A173" s="32" t="s">
-        <v>424</v>
-      </c>
-      <c r="B173" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="C173" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D173" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E173" s="34" t="b">
-        <v>0</v>
+    <row r="173" spans="1:15" s="8" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D173" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E173" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="F173" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="G173" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H173" s="33"/>
-      <c r="I173" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J173" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K173" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L173" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M173" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N173" s="13"/>
+      <c r="G173" s="7"/>
+      <c r="H173" s="7"/>
+      <c r="I173" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J173" s="6">
+        <v>68</v>
+      </c>
+      <c r="K173" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L173" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M173" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N173" s="7"/>
       <c r="O173" s="7" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A174" s="32" t="s">
-        <v>433</v>
-      </c>
-      <c r="B174" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="C174" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="D174" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E174" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="F174" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G174" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H174" s="33"/>
-      <c r="I174" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J174" s="6">
-        <v>64</v>
-      </c>
-      <c r="K174" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="L174" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M174" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="N174" s="26"/>
-      <c r="O174" s="7"/>
-    </row>
-    <row r="175" spans="1:15" s="8" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="14" t="s">
-        <v>443</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D175" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E175" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F175" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G175" s="7"/>
-      <c r="H175" s="7"/>
-      <c r="I175" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J175" s="6">
-        <v>68</v>
-      </c>
-      <c r="K175" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L175" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="M175" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="N175" s="7"/>
-      <c r="O175" s="7" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O174">
-      <sortCondition ref="B1:B174"/>
+  <autoFilter ref="A1:O173" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O172">
+      <sortCondition ref="B1:B172"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
